--- a/outputs/QLD_historical_prices.xlsx
+++ b/outputs/QLD_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62.04</v>
+        <v>61.64</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>57.65</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62.67</v>
+        <v>62.16</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>58.2</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>82.02</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88</v>
+        <v>88.38</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>84.79000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>91.12</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>86.89</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>94.03</v>
+        <v>93.81</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.04000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>98.64</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>112.74</v>
+        <v>112.71</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>127.88</v>
+        <v>127.69</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>124.84</v>
+        <v>124.62</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>142.18</v>
+        <v>141.79</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>93.28</v>
+        <v>93.31</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>107.83</v>
+        <v>107.73</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>110.22</v>
+        <v>110.12</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>127.85</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Aug 2026</t>
+          <t>Data through: Sep 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6333,6 +6333,26 @@
       </c>
       <c r="F279" s="7" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="F280" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6344,7 +6364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11663,8 +11683,27 @@
         <v>61.72</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>40.93</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B279">
+  <conditionalFormatting sqref="B2:B280">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11676,7 +11715,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C279">
+  <conditionalFormatting sqref="C2:C280">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11688,7 +11727,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D279">
+  <conditionalFormatting sqref="D2:D280">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11700,7 +11739,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E279">
+  <conditionalFormatting sqref="E2:E280">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/QLD_historical_prices.xlsx
+++ b/outputs/QLD_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>61.64</v>
+        <v>65.12</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>57.65</v>
+        <v>61.37</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62.16</v>
+        <v>65.53</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>58.11</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>82.02</v>
+        <v>83.13</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88.38</v>
+        <v>89.56</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>84.67</v>
+        <v>85.61</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>91.43000000000001</v>
+        <v>92.45</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>86.84999999999999</v>
+        <v>88.53</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>93.81</v>
+        <v>95.41</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>90.88</v>
+        <v>92.47</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>98.3</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>112.71</v>
+        <v>113.22</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>127.69</v>
+        <v>127.84</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>124.62</v>
+        <v>124.88</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>141.79</v>
+        <v>141.65</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>93.31</v>
+        <v>93.67</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>107.73</v>
+        <v>107.97</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>110.12</v>
+        <v>110.33</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>127.6</v>
+        <v>127.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Sep 2026</t>
+          <t>Data through: Oct 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F280"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6353,6 +6353,26 @@
       </c>
       <c r="F280" s="7" t="inlineStr"/>
     </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="F281" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6364,7 +6384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E280"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11702,8 +11722,27 @@
         <v>40.93</v>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>89.76000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B280">
+  <conditionalFormatting sqref="B2:B281">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11715,7 +11754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C280">
+  <conditionalFormatting sqref="C2:C281">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11727,7 +11766,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D280">
+  <conditionalFormatting sqref="D2:D281">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11739,7 +11778,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E280">
+  <conditionalFormatting sqref="E2:E281">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
